--- a/salesforce_forms/027_vacation_bible_school_signup_form--salesforce_forms.xlsx
+++ b/salesforce_forms/027_vacation_bible_school_signup_form--salesforce_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -784,8 +784,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -813,12 +813,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{1:_1,_'name':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{1: 1, 'name': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{2:_2,_'name':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{2: 2, 'name': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{3:_3,_'name':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{3: 3, 'name': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{4:_4,_'name':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{4: 4, 'name': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{5:_5,_'name':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{5: 5, 'name': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{6:_6,_'name':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{6: 6, 'name': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{7:_7,_'name':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{7: 7, 'name': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{8:_8,_'name':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{8: 8, 'name': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{9:_9,_'name':_9}</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{9: 9, 'name': 9}</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{10:_10,_'name':_10}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{10: 10, 'name': 10}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{1:_1,_'name':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{1: 1, 'name': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{2:_2,_'name':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{2: 2, 'name': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{3:_3,_'name':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{3: 3, 'name': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{4:_4,_'name':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{4: 4, 'name': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{5:_5,_'name':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{5: 5, 'name': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{6:_6,_'name':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{6: 6, 'name': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{7:_7,_'name':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{7: 7, 'name': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{8:_8,_'name':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{8: 8, 'name': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{9:_9,_'name':_9}</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{9: 9, 'name': 9}</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{10:_10,_'name':_10}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{10: 10, 'name': 10}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
